--- a/APIS.xlsx
+++ b/APIS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My project\DTB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA73854-9FED-43E8-90A0-2D6F38D2DC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D48357-B13E-4EB6-8A34-7B5B204617F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{75D59F26-9101-4F9B-8527-107521FAB567}"/>
   </bookViews>
@@ -62,109 +62,70 @@
     <t>/</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/nhan-vien</t>
-  </si>
-  <si>
     <t>Xem chi tiết 1 nhân viên</t>
   </si>
   <si>
     <t>/:maNV</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/nhan-vien/NV001</t>
-  </si>
-  <si>
     <t>2. /api/nguyen-lieu</t>
   </si>
   <si>
     <t>Lấy danh sách tất cả nguyên liệu</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/nguyen-lieu</t>
-  </si>
-  <si>
     <t>Cảnh báo: Nguyên liệu sắp hết (&lt; 20)</t>
   </si>
   <si>
     <t>/sap-het</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/nguyen-lieu/sap-het</t>
-  </si>
-  <si>
     <t>3./api/mon-an</t>
   </si>
   <si>
     <t>Lấy toàn bộ thực đơn</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/mon-an</t>
-  </si>
-  <si>
     <t>Tìm kiếm món ăn theo tên</t>
   </si>
   <si>
     <t>/tim-kiem?ten=...</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/mon-an/tim-kiem?ten=Phở</t>
-  </si>
-  <si>
     <t>Xem chi tiết món (kèm công thức)</t>
   </si>
   <si>
     <t>/:maMon</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/mon-an/MA01</t>
-  </si>
-  <si>
     <t>4. /api/nha-cung-cap</t>
   </si>
   <si>
     <t>Lấy danh sách đối tác</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/nha-cung-cap</t>
-  </si>
-  <si>
     <t>Xem chi tiết nhà cung cấp</t>
   </si>
   <si>
     <t>/:maNCC</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/nha-cung-cap/NCC01</t>
-  </si>
-  <si>
     <t>5. /api/hoa-don</t>
   </si>
   <si>
     <t>Lấy lịch sử hóa đơn bán hàng</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/hoa-don</t>
-  </si>
-  <si>
     <t>Xem chi tiết hóa đơn (kèm món ăn)</t>
   </si>
   <si>
     <t>/chi-tiet/:maHD</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/hoa-don/chi-tiet/HD001</t>
-  </si>
-  <si>
     <t>/thong-ke/doanh-thu</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/hoa-don/thong-ke/doanh-thu?thang=1&amp;nam=2024</t>
-  </si>
-  <si>
     <t>/thong-ke/nhan-vien</t>
-  </si>
-  <si>
-    <t>http://localhost:3000/api/hoa-don/thong-ke/nhan-vien</t>
   </si>
   <si>
     <r>
@@ -201,22 +162,13 @@
     <t>Lấy danh sách đơn nhập hàng</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/don-hang</t>
-  </si>
-  <si>
     <t>Xem chi tiết đơn nhập hàng</t>
   </si>
   <si>
     <t>/:maDH</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/don-hang/DH001</t>
-  </si>
-  <si>
     <t>/thong-ke/chi-phi-nhap</t>
-  </si>
-  <si>
-    <t>http://localhost:3000/api/don-hang/thong-ke/chi-phi-nhap</t>
   </si>
   <si>
     <r>
@@ -239,58 +191,37 @@
     <t>Lấy danh sách các Ca (Sáng/Chiều...)</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/ca-lam-viec</t>
-  </si>
-  <si>
     <t>Xem toàn bộ lịch phân công</t>
   </si>
   <si>
     <t>/phan-cong</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/ca-lam-viec/phan-cong</t>
-  </si>
-  <si>
     <t>Xem phân công theo ngày cụ thể</t>
   </si>
   <si>
     <t>/phan-cong/tim-kiem</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/ca-lam-viec/phan-cong/tim-kiem?ngay=2024-12-03</t>
-  </si>
-  <si>
     <t>8. /api/lich-lam-viec</t>
   </si>
   <si>
     <t>Xem lịch làm việc (kèm tên NV)</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/lich-lam-viec</t>
-  </si>
-  <si>
     <t>Xem lịch riêng của 1 nhân viên</t>
   </si>
   <si>
     <t>/nhan-vien/:maNV</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/lich-lam-viec/nhan-vien/NV001</t>
-  </si>
-  <si>
     <t>Xem bảng chấm công thực tế</t>
   </si>
   <si>
     <t>/cham-cong</t>
   </si>
   <si>
-    <t>http://localhost:3000/api/lich-lam-viec/cham-cong</t>
-  </si>
-  <si>
     <t>/cham-cong/thong-ke</t>
-  </si>
-  <si>
-    <t>http://localhost:3000/api/lich-lam-viec/cham-cong/thong-ke</t>
   </si>
   <si>
     <r>
@@ -305,6 +236,75 @@
       </rPr>
       <t xml:space="preserve"> Trạng thái đi làm</t>
     </r>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/nhan-vien</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/nhan-vien/NV001</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/nguyen-lieu</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/nguyen-lieu/sap-het</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/mon-an</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/mon-an/tim-kiem?ten=Phở</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/mon-an/MA01</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/nha-cung-cap</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/nha-cung-cap/NCC01</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/hoa-don</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/hoa-don/chi-tiet/HD001</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/hoa-don/thong-ke/doanh-thu?thang=1&amp;nam=2024</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/hoa-don/thong-ke/nhan-vien</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/don-hang</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/don-hang/DH001</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/don-hang/thong-ke/chi-phi-nhap</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/ca-lam-viec</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/ca-lam-viec/phan-cong</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/ca-lam-viec/phan-cong/tim-kiem?ngay=2024-12-03</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/lich-lam-viec</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/lich-lam-viec/nhan-vien/NV001</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/lich-lam-viec/cham-cong</t>
+  </si>
+  <si>
+    <t>http://qlbep.onrender.com/api/lich-lam-viec/cham-cong/thong-ke</t>
   </si>
 </sst>
 </file>
@@ -417,13 +417,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -435,9 +432,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -448,6 +442,18 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -794,170 +800,170 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="23.65" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="22.15" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="22.15" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.4">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="26.25" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="18">
-      <c r="A6" s="2" t="s">
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30.4">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.4">
-      <c r="A7" s="4" t="s">
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18">
+      <c r="A11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.4">
+      <c r="A12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="26.25" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.75">
+      <c r="A13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30.4">
-      <c r="A9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="30.4">
+      <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="B14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="18">
-      <c r="A11" s="2" t="s">
+      <c r="D14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="30.4">
+      <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.4">
-      <c r="A12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.75">
-      <c r="A13" s="5" t="s">
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="30.4">
-      <c r="A14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="30.4">
-      <c r="A15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>26</v>
+      <c r="D15" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="E15" s="1"/>
     </row>
@@ -969,55 +975,55 @@
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" ht="17.649999999999999">
-      <c r="A17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="A17" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
     </row>
     <row r="18" spans="1:5" ht="15.4">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5" ht="15.75">
-      <c r="A19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="A19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>29</v>
+      <c r="D19" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" ht="15.75">
-      <c r="A20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>32</v>
+      <c r="A20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="E20" s="1"/>
     </row>
@@ -1029,275 +1035,275 @@
       <c r="E21" s="1"/>
     </row>
     <row r="22" spans="1:5" ht="18">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15">
+      <c r="A23" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15">
+      <c r="A24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="30">
+      <c r="A25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="30">
+      <c r="A26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="30">
+      <c r="A27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="18">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15">
+      <c r="A31" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15">
+      <c r="A32" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="15">
-      <c r="A23" s="8" t="s">
+      <c r="B32" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="30">
+      <c r="A33" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="30">
+      <c r="A34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18">
+      <c r="A36" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15">
+      <c r="A37" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B37" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D37" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15">
-      <c r="A24" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="10" t="s">
+    <row r="38" spans="1:4" ht="30">
+      <c r="A38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="30">
-      <c r="A25" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="30">
-      <c r="A26" s="8" t="s">
+      <c r="D38" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="30">
+      <c r="A39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="30">
+      <c r="A40" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="30">
-      <c r="A27" s="8" t="s">
+      <c r="D40" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="17.649999999999999">
+      <c r="A42" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="18">
-      <c r="A30" s="3" t="s">
+    </row>
+    <row r="43" spans="1:4" ht="15">
+      <c r="A43" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15">
+      <c r="A44" s="7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="15">
-      <c r="A31" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15">
-      <c r="A32" s="9" t="s">
+      <c r="B44" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="30">
+      <c r="A45" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="B45" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="30">
-      <c r="A33" s="9" t="s">
+      <c r="D45" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="30">
+      <c r="A46" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="10" t="s">
+      <c r="B46" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D46" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="30">
+      <c r="A47" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="30">
-      <c r="A34" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="18">
-      <c r="A36" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15">
-      <c r="A37" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="30">
-      <c r="A38" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="30">
-      <c r="A39" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="30">
-      <c r="A40" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="17.649999999999999">
-      <c r="A42" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15">
-      <c r="A43" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15">
-      <c r="A44" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="30">
-      <c r="A45" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="30">
-      <c r="A46" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="30">
-      <c r="A47" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1308,17 +1314,18 @@
     <mergeCell ref="A17:D17"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{D7C2FE60-318C-4A26-A1B1-33661A86FC9F}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{09DD58A7-7D38-423D-BEC1-62A75AA01505}"/>
-    <hyperlink ref="D8" r:id="rId3" xr:uid="{4E636F71-70F8-43C3-B462-0926768D9422}"/>
-    <hyperlink ref="D9" r:id="rId4" xr:uid="{8DD9FE02-8A1B-4231-B2B3-E5F31F602B10}"/>
-    <hyperlink ref="D13" r:id="rId5" xr:uid="{2B0EF2E5-ED7D-4BD1-9F61-02B4A1252709}"/>
-    <hyperlink ref="D14" r:id="rId6" xr:uid="{88FA6FB1-87E3-4113-9053-1B2C935F842C}"/>
-    <hyperlink ref="D15" r:id="rId7" xr:uid="{5815A278-B323-4DD3-9D66-078A997A7036}"/>
-    <hyperlink ref="D19" r:id="rId8" xr:uid="{18007C84-D092-49FE-9014-C4C29E3CA4A0}"/>
-    <hyperlink ref="D20" r:id="rId9" xr:uid="{B4919BBF-A465-40F2-B8F4-8F31F20EB1CC}"/>
+    <hyperlink ref="D3" r:id="rId1" display="http://localhost:3000/api/nhan-vien" xr:uid="{D7C2FE60-318C-4A26-A1B1-33661A86FC9F}"/>
+    <hyperlink ref="D4" r:id="rId2" display="http://localhost:3000/api/nhan-vien/NV001" xr:uid="{09DD58A7-7D38-423D-BEC1-62A75AA01505}"/>
+    <hyperlink ref="D8" r:id="rId3" display="http://localhost:3000/api/nguyen-lieu" xr:uid="{4E636F71-70F8-43C3-B462-0926768D9422}"/>
+    <hyperlink ref="D9" r:id="rId4" display="http://localhost:3000/api/nguyen-lieu/sap-het" xr:uid="{8DD9FE02-8A1B-4231-B2B3-E5F31F602B10}"/>
+    <hyperlink ref="D13" r:id="rId5" display="http://localhost:3000/api/mon-an" xr:uid="{2B0EF2E5-ED7D-4BD1-9F61-02B4A1252709}"/>
+    <hyperlink ref="D14" r:id="rId6" display="http://localhost:3000/api/mon-an/tim-kiem?ten=Phở" xr:uid="{88FA6FB1-87E3-4113-9053-1B2C935F842C}"/>
+    <hyperlink ref="D15" r:id="rId7" display="http://localhost:3000/api/mon-an/MA01" xr:uid="{5815A278-B323-4DD3-9D66-078A997A7036}"/>
+    <hyperlink ref="D19" r:id="rId8" display="http://localhost:3000/api/nha-cung-cap" xr:uid="{18007C84-D092-49FE-9014-C4C29E3CA4A0}"/>
+    <hyperlink ref="D20" r:id="rId9" display="http://localhost:3000/api/nha-cung-cap/NCC01" xr:uid="{B4919BBF-A465-40F2-B8F4-8F31F20EB1CC}"/>
+    <hyperlink ref="D24" r:id="rId10" xr:uid="{E1D1A921-A02B-417F-9AD1-8652593DFB5D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>